--- a/EDA/EDA_Updated.xlsx
+++ b/EDA/EDA_Updated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fc4bd521ffc22738/Desktop/Freelancing/AIGEN/smartsentry_aml_model/EDA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="83" documentId="11_312311E4919401CF5C5916020C08ACC1C8AF9D0E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D430EBE-08D8-428C-8A5C-59473126FA90}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="14_{6497EF10-EDC5-4865-9BC0-F367B6DE2175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{068B504D-5FF4-47DA-BB28-CCE1279B1886}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="7" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1_Overview" sheetId="1" r:id="rId1"/>
@@ -4021,14 +4021,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -28872,8 +28872,8 @@
     <col min="7" max="7" width="16" style="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="36" x14ac:dyDescent="0.3">
-      <c r="A1" s="74" t="s">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="76" t="s">
         <v>818</v>
       </c>
     </row>
@@ -29113,7 +29113,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="75" t="s">
+      <c r="A14" s="74" t="s">
         <v>296</v>
       </c>
       <c r="B14" s="27">
@@ -29136,7 +29136,7 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="75" t="s">
+      <c r="A15" s="74" t="s">
         <v>326</v>
       </c>
       <c r="B15" s="27">
@@ -29159,7 +29159,7 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="75" t="s">
+      <c r="A16" s="74" t="s">
         <v>278</v>
       </c>
       <c r="B16" s="27">
@@ -29182,7 +29182,7 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="75" t="s">
+      <c r="A17" s="74" t="s">
         <v>256</v>
       </c>
       <c r="B17" s="27">
@@ -29205,7 +29205,7 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="75" t="s">
+      <c r="A18" s="74" t="s">
         <v>334</v>
       </c>
       <c r="B18" s="27">
@@ -29228,7 +29228,7 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="75" t="s">
+      <c r="A19" s="74" t="s">
         <v>344</v>
       </c>
       <c r="B19" s="27">
@@ -29251,7 +29251,7 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="75" t="s">
+      <c r="A20" s="74" t="s">
         <v>318</v>
       </c>
       <c r="B20" s="27">
@@ -29274,7 +29274,7 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="75" t="s">
+      <c r="A21" s="74" t="s">
         <v>300</v>
       </c>
       <c r="B21" s="27">
@@ -29297,7 +29297,7 @@
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="75" t="s">
+      <c r="A22" s="74" t="s">
         <v>266</v>
       </c>
       <c r="B22" s="27">
@@ -29320,7 +29320,7 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="75" t="s">
+      <c r="A23" s="74" t="s">
         <v>332</v>
       </c>
       <c r="B23" s="27">
@@ -29343,7 +29343,7 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="75" t="s">
+      <c r="A24" s="74" t="s">
         <v>288</v>
       </c>
       <c r="B24" s="27">
@@ -29366,7 +29366,7 @@
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="75" t="s">
+      <c r="A25" s="74" t="s">
         <v>298</v>
       </c>
       <c r="B25" s="27">
@@ -29389,7 +29389,7 @@
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="75" t="s">
+      <c r="A26" s="74" t="s">
         <v>284</v>
       </c>
       <c r="B26" s="27">
@@ -29412,7 +29412,7 @@
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="75" t="s">
+      <c r="A27" s="74" t="s">
         <v>330</v>
       </c>
       <c r="B27" s="27">
@@ -29435,7 +29435,7 @@
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="75" t="s">
+      <c r="A28" s="74" t="s">
         <v>302</v>
       </c>
       <c r="B28" s="27">
@@ -29458,7 +29458,7 @@
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="75" t="s">
+      <c r="A29" s="74" t="s">
         <v>258</v>
       </c>
       <c r="B29" s="27">
@@ -29481,7 +29481,7 @@
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="75" t="s">
+      <c r="A30" s="74" t="s">
         <v>316</v>
       </c>
       <c r="B30" s="27">
@@ -29504,7 +29504,7 @@
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="75" t="s">
+      <c r="A31" s="74" t="s">
         <v>290</v>
       </c>
       <c r="B31" s="27">
@@ -29527,7 +29527,7 @@
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="75" t="s">
+      <c r="A32" s="74" t="s">
         <v>286</v>
       </c>
       <c r="B32" s="27">
@@ -29550,7 +29550,7 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="75" t="s">
+      <c r="A33" s="74" t="s">
         <v>280</v>
       </c>
       <c r="B33" s="27">
@@ -29573,7 +29573,7 @@
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="75" t="s">
+      <c r="A34" s="74" t="s">
         <v>264</v>
       </c>
       <c r="B34" s="27">
@@ -29596,7 +29596,7 @@
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="75" t="s">
+      <c r="A35" s="74" t="s">
         <v>328</v>
       </c>
       <c r="B35" s="27">
@@ -29619,7 +29619,7 @@
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="75" t="s">
+      <c r="A36" s="74" t="s">
         <v>322</v>
       </c>
       <c r="B36" s="27">
@@ -29642,7 +29642,7 @@
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="75" t="s">
+      <c r="A37" s="74" t="s">
         <v>324</v>
       </c>
       <c r="B37" s="27">
@@ -29665,7 +29665,7 @@
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="75" t="s">
+      <c r="A38" s="74" t="s">
         <v>304</v>
       </c>
       <c r="B38" s="27">
@@ -29688,7 +29688,7 @@
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="75" t="s">
+      <c r="A39" s="74" t="s">
         <v>274</v>
       </c>
       <c r="B39" s="27">
@@ -29711,7 +29711,7 @@
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="75" t="s">
+      <c r="A40" s="74" t="s">
         <v>292</v>
       </c>
       <c r="B40" s="27">
@@ -30095,7 +30095,7 @@
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" s="76" t="s">
+      <c r="A60" s="75" t="s">
         <v>719</v>
       </c>
       <c r="B60" s="28">
